--- a/Assets/Data/Datatable.xlsx
+++ b/Assets/Data/Datatable.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\RPG - コピー\Assets\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\RPG\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E822C677-14D2-4478-892A-BCB0F56AB2BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0943BB64-DBEC-477A-B366-B734311B0F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{1A0CE3EC-C9BF-49DF-A1BD-F2CBB20E8474}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{1A0CE3EC-C9BF-49DF-A1BD-F2CBB20E8474}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerData" sheetId="8" r:id="rId1"/>
@@ -625,9 +625,6 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>arm002</t>
-  </si>
-  <si>
     <t>arm003</t>
   </si>
   <si>
@@ -1635,6 +1632,10 @@
     <rPh sb="2" eb="3">
       <t>イシ</t>
     </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>arm002</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -4071,7 +4072,7 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.4">
       <c r="B1" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
@@ -4101,7 +4102,7 @@
       <c r="C2" s="153"/>
       <c r="D2" s="154"/>
       <c r="E2" s="155" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F2" s="156"/>
       <c r="G2" s="156"/>
@@ -4115,75 +4116,75 @@
       <c r="O2" s="156"/>
       <c r="P2" s="156"/>
       <c r="Q2" s="149" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="R2" s="150"/>
       <c r="S2" s="150"/>
       <c r="T2" s="151"/>
       <c r="U2" s="83" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.4">
       <c r="B3" s="81" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C3" s="81" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D3" s="81" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E3" s="82" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F3" s="82" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G3" s="82" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H3" s="82" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I3" s="82" t="s">
+        <v>212</v>
+      </c>
+      <c r="J3" s="82" t="s">
         <v>213</v>
       </c>
-      <c r="J3" s="82" t="s">
-        <v>214</v>
-      </c>
       <c r="K3" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L3" s="82" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M3" s="82" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="N3" s="82" t="s">
+        <v>223</v>
+      </c>
+      <c r="O3" s="82" t="s">
         <v>224</v>
       </c>
-      <c r="O3" s="82" t="s">
-        <v>225</v>
-      </c>
       <c r="P3" s="82" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q3" s="82" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="R3" s="84" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S3" s="84" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="T3" s="25" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="U3" s="85" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.4">
@@ -4192,66 +4193,66 @@
         <v>0</v>
       </c>
       <c r="C4" s="124" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D4" s="24" t="s">
         <v>1</v>
       </c>
       <c r="E4" s="77" t="s">
+        <v>207</v>
+      </c>
+      <c r="F4" s="77" t="s">
         <v>208</v>
       </c>
-      <c r="F4" s="77" t="s">
-        <v>209</v>
-      </c>
       <c r="G4" s="77" t="s">
+        <v>210</v>
+      </c>
+      <c r="H4" s="77" t="s">
         <v>211</v>
       </c>
-      <c r="H4" s="77" t="s">
-        <v>212</v>
-      </c>
       <c r="I4" s="79" t="s">
+        <v>214</v>
+      </c>
+      <c r="J4" s="79" t="s">
         <v>215</v>
       </c>
-      <c r="J4" s="79" t="s">
-        <v>216</v>
-      </c>
       <c r="K4" s="80" t="s">
+        <v>217</v>
+      </c>
+      <c r="L4" s="80" t="s">
         <v>218</v>
       </c>
-      <c r="L4" s="80" t="s">
-        <v>219</v>
-      </c>
       <c r="M4" s="79" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="N4" s="79" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O4" s="79" t="s">
+        <v>225</v>
+      </c>
+      <c r="P4" s="79" t="s">
         <v>226</v>
-      </c>
-      <c r="P4" s="79" t="s">
-        <v>227</v>
       </c>
       <c r="Q4" s="109" t="s">
         <v>33</v>
       </c>
       <c r="R4" s="108" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="S4" s="108" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="T4" s="110" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="U4" s="85" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.4">
       <c r="B5" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C5" s="3">
         <v>1</v>
@@ -4305,7 +4306,7 @@
         <v>99</v>
       </c>
       <c r="T5" s="41" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="U5" s="113" t="s">
         <v>16</v>
@@ -4421,7 +4422,7 @@
   <sheetData>
     <row r="1" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" spans="2:2" x14ac:dyDescent="0.4">
@@ -4476,7 +4477,7 @@
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B14" s="29" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.4">
@@ -4491,7 +4492,7 @@
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B17" s="28" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.4">
@@ -4546,52 +4547,52 @@
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B30" s="70" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B31" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="32" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B32" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B33" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B34" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B36" s="111" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="37" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B37" s="28" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="38" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B38" s="28" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B39" s="28" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="40" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B40" s="28" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -4614,7 +4615,7 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.4">
       <c r="B1" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
@@ -4646,46 +4647,46 @@
       <c r="K2" s="163"/>
       <c r="L2" s="163"/>
       <c r="M2" s="90" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A3" s="6"/>
       <c r="B3" s="86" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C3" s="87" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D3" s="87" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E3" s="88" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F3" s="88" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G3" s="88" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H3" s="88" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I3" s="88" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J3" s="88" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K3" s="88" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="L3" s="89" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M3" s="91" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.4">
@@ -4694,7 +4695,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="125" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D4" s="24" t="s">
         <v>1</v>
@@ -4724,12 +4725,12 @@
         <v>33</v>
       </c>
       <c r="M4" s="83" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
       <c r="B5" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C5" s="3">
         <v>1</v>
@@ -4767,7 +4768,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.4">
       <c r="B6" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C6" s="3">
         <v>1</v>
@@ -4805,7 +4806,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
       <c r="B7" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C7" s="3">
         <v>1</v>
@@ -4947,7 +4948,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.4">
       <c r="B1" s="32" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
@@ -4974,25 +4975,25 @@
     <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A3" s="33"/>
       <c r="B3" s="95" t="s">
+        <v>153</v>
+      </c>
+      <c r="C3" s="74" t="s">
+        <v>232</v>
+      </c>
+      <c r="D3" s="74" t="s">
         <v>154</v>
       </c>
-      <c r="C3" s="74" t="s">
-        <v>233</v>
-      </c>
-      <c r="D3" s="74" t="s">
+      <c r="E3" s="92" t="s">
         <v>155</v>
       </c>
-      <c r="E3" s="92" t="s">
+      <c r="F3" s="93" t="s">
+        <v>181</v>
+      </c>
+      <c r="G3" s="93" t="s">
         <v>156</v>
       </c>
-      <c r="F3" s="93" t="s">
-        <v>182</v>
-      </c>
-      <c r="G3" s="93" t="s">
+      <c r="H3" s="94" t="s">
         <v>157</v>
-      </c>
-      <c r="H3" s="94" t="s">
-        <v>158</v>
       </c>
       <c r="I3" s="34"/>
     </row>
@@ -5002,7 +5003,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="74" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D4" s="123" t="s">
         <v>28</v>
@@ -5023,19 +5024,19 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.4">
       <c r="B5" s="28" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C5" s="28">
         <v>2</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E5" s="28" t="s">
         <v>34</v>
       </c>
       <c r="F5" s="28" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G5" s="28">
         <v>1</v>
@@ -5047,16 +5048,16 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="B6" s="128" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C6" s="128">
         <v>2</v>
       </c>
       <c r="D6" s="128" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E6" s="128" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F6" s="128" t="s">
         <v>39</v>
@@ -5071,13 +5072,13 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.4">
       <c r="B7" s="128" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C7" s="128">
         <v>2</v>
       </c>
       <c r="D7" s="128" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E7" s="128" t="s">
         <v>36</v>
@@ -5095,13 +5096,13 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.4">
       <c r="B8" s="28" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C8" s="28">
         <v>2</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E8" s="28" t="s">
         <v>46</v>
@@ -5119,13 +5120,13 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.4">
       <c r="B9" s="128" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C9" s="128">
         <v>2</v>
       </c>
       <c r="D9" s="128" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E9" s="128" t="s">
         <v>34</v>
@@ -5143,13 +5144,13 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.4">
       <c r="B10" s="128" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C10" s="128">
         <v>2</v>
       </c>
       <c r="D10" s="128" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E10" s="128" t="s">
         <v>36</v>
@@ -5167,13 +5168,13 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.4">
       <c r="B11" s="128" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C11" s="128">
         <v>2</v>
       </c>
       <c r="D11" s="128" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E11" s="128" t="s">
         <v>37</v>
@@ -5191,13 +5192,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.4">
       <c r="B12" s="28" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C12" s="28">
         <v>2</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E12" s="28" t="s">
         <v>50</v>
@@ -5260,7 +5261,7 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B1" s="32" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
@@ -5280,7 +5281,7 @@
       <c r="C2" s="145"/>
       <c r="D2" s="146"/>
       <c r="E2" s="72" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F2" s="147" t="s">
         <v>49</v>
@@ -5295,34 +5296,34 @@
     <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3" s="33"/>
       <c r="B3" s="96" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C3" s="74" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D3" s="97" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E3" s="93" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F3" s="79" t="s">
+        <v>162</v>
+      </c>
+      <c r="G3" s="79" t="s">
         <v>163</v>
       </c>
-      <c r="G3" s="79" t="s">
+      <c r="H3" s="98" t="s">
         <v>164</v>
       </c>
-      <c r="H3" s="98" t="s">
+      <c r="I3" s="98" t="s">
         <v>165</v>
       </c>
-      <c r="I3" s="98" t="s">
+      <c r="J3" s="79" t="s">
+        <v>142</v>
+      </c>
+      <c r="K3" s="98" t="s">
         <v>166</v>
-      </c>
-      <c r="J3" s="79" t="s">
-        <v>143</v>
-      </c>
-      <c r="K3" s="98" t="s">
-        <v>167</v>
       </c>
       <c r="L3" s="34"/>
     </row>
@@ -5332,13 +5333,13 @@
         <v>0</v>
       </c>
       <c r="C4" s="74" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D4" s="37" t="s">
         <v>1</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F4" s="26" t="s">
         <v>56</v>
@@ -5353,7 +5354,7 @@
         <v>45</v>
       </c>
       <c r="J4" s="26" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K4" s="39" t="s">
         <v>54</v>
@@ -5362,13 +5363,13 @@
     </row>
     <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
       <c r="B5" s="44" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C5" s="44">
         <v>3</v>
       </c>
       <c r="D5" s="45" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E5" s="46" t="s">
         <v>34</v>
@@ -5387,7 +5388,7 @@
       </c>
       <c r="J5" s="143"/>
       <c r="K5" s="45" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.4">
@@ -5404,7 +5405,7 @@
         <v>34</v>
       </c>
       <c r="F6" s="46" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G6" s="114">
         <v>1</v>
@@ -5552,13 +5553,13 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B11" s="28" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C11" s="28">
         <v>3</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E11" s="41" t="s">
         <v>46</v>
@@ -5712,7 +5713,7 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.4">
       <c r="B1" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
@@ -5753,43 +5754,43 @@
     <row r="3" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A3" s="6"/>
       <c r="B3" s="99" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C3" s="87" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D3" s="100" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E3" s="93" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F3" s="82" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G3" s="82" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H3" s="82" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I3" s="82" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J3" s="79" t="s">
+        <v>167</v>
+      </c>
+      <c r="K3" s="98" t="s">
+        <v>165</v>
+      </c>
+      <c r="L3" s="79" t="s">
         <v>168</v>
       </c>
-      <c r="K3" s="98" t="s">
+      <c r="M3" s="79" t="s">
+        <v>164</v>
+      </c>
+      <c r="N3" s="98" t="s">
         <v>166</v>
-      </c>
-      <c r="L3" s="79" t="s">
-        <v>169</v>
-      </c>
-      <c r="M3" s="79" t="s">
-        <v>165</v>
-      </c>
-      <c r="N3" s="98" t="s">
-        <v>167</v>
       </c>
       <c r="O3" s="5"/>
     </row>
@@ -5799,13 +5800,13 @@
         <v>0</v>
       </c>
       <c r="C4" s="125" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D4" s="57" t="s">
         <v>1</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F4" s="26" t="s">
         <v>85</v>
@@ -5826,13 +5827,13 @@
         <v>45</v>
       </c>
       <c r="L4" s="26" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="M4" s="26" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="39" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O4" s="5"/>
     </row>
@@ -5961,7 +5962,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="60" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E8" s="60" t="s">
         <v>37</v>
@@ -5994,13 +5995,13 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.4">
       <c r="B9" s="3" t="s">
-        <v>95</v>
+        <v>292</v>
       </c>
       <c r="C9" s="3">
         <v>3</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>37</v>
@@ -6033,13 +6034,13 @@
     </row>
     <row r="10" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B10" s="59" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C10" s="59">
         <v>3</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>37</v>
@@ -6078,7 +6079,7 @@
         <v>3</v>
       </c>
       <c r="D11" s="58" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E11" s="58" t="s">
         <v>50</v>
@@ -6111,13 +6112,13 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.4">
       <c r="B12" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C12" s="3">
         <v>3</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>50</v>
@@ -6269,7 +6270,7 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B1" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
@@ -6284,12 +6285,12 @@
     <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2" s="6"/>
       <c r="B2" s="174" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C2" s="174"/>
       <c r="D2" s="175"/>
       <c r="E2" s="172" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F2" s="173"/>
       <c r="G2" s="173"/>
@@ -6301,50 +6302,50 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B3" s="102" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C3" s="87" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D3" s="103" t="s">
+        <v>160</v>
+      </c>
+      <c r="E3" s="104" t="s">
+        <v>171</v>
+      </c>
+      <c r="F3" s="104" t="s">
         <v>161</v>
       </c>
-      <c r="E3" s="104" t="s">
+      <c r="G3" s="104" t="s">
+        <v>163</v>
+      </c>
+      <c r="H3" s="104" t="s">
         <v>172</v>
       </c>
-      <c r="F3" s="104" t="s">
-        <v>162</v>
-      </c>
-      <c r="G3" s="104" t="s">
+      <c r="I3" s="104" t="s">
         <v>164</v>
       </c>
-      <c r="H3" s="104" t="s">
+      <c r="J3" s="104" t="s">
         <v>173</v>
       </c>
-      <c r="I3" s="104" t="s">
-        <v>165</v>
-      </c>
-      <c r="J3" s="104" t="s">
-        <v>174</v>
-      </c>
       <c r="K3" s="121" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L3" s="122"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4" s="6"/>
       <c r="B4" s="69" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="125" t="s">
+        <v>231</v>
+      </c>
+      <c r="D4" s="101" t="s">
         <v>103</v>
       </c>
-      <c r="C4" s="125" t="s">
-        <v>232</v>
-      </c>
-      <c r="D4" s="101" t="s">
+      <c r="E4" s="79" t="s">
         <v>104</v>
-      </c>
-      <c r="E4" s="79" t="s">
-        <v>105</v>
       </c>
       <c r="F4" s="80" t="s">
         <v>56</v>
@@ -6353,34 +6354,34 @@
         <v>77</v>
       </c>
       <c r="H4" s="80" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I4" s="80" t="s">
+        <v>105</v>
+      </c>
+      <c r="J4" s="79" t="s">
         <v>106</v>
       </c>
-      <c r="J4" s="79" t="s">
+      <c r="K4" s="98" t="s">
         <v>107</v>
-      </c>
-      <c r="K4" s="98" t="s">
-        <v>108</v>
       </c>
       <c r="L4" s="68"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B5" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C5" s="3">
         <v>4</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G5" s="3">
         <v>5</v>
@@ -6398,19 +6399,19 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B6" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C6" s="3">
         <v>4</v>
       </c>
       <c r="D6" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>114</v>
       </c>
       <c r="G6" s="3">
         <v>2</v>
@@ -6465,7 +6466,7 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B1" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
@@ -6498,34 +6499,34 @@
     <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3" s="6"/>
       <c r="B3" s="75" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C3" s="87" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D3" s="76" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E3" s="71" t="s">
+        <v>174</v>
+      </c>
+      <c r="F3" s="72" t="s">
         <v>175</v>
       </c>
-      <c r="F3" s="72" t="s">
+      <c r="G3" s="72" t="s">
         <v>176</v>
       </c>
-      <c r="G3" s="72" t="s">
+      <c r="H3" s="72" t="s">
         <v>177</v>
       </c>
-      <c r="H3" s="72" t="s">
+      <c r="I3" s="72" t="s">
         <v>178</v>
       </c>
-      <c r="I3" s="72" t="s">
+      <c r="J3" s="72" t="s">
         <v>179</v>
       </c>
-      <c r="J3" s="72" t="s">
+      <c r="K3" s="73" t="s">
         <v>180</v>
-      </c>
-      <c r="K3" s="73" t="s">
-        <v>181</v>
       </c>
       <c r="L3" s="5"/>
     </row>
@@ -6535,7 +6536,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="125" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D4" s="103" t="s">
         <v>1</v>
@@ -6565,7 +6566,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C5" s="4">
         <v>5</v>
@@ -6597,7 +6598,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B6" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C6" s="4">
         <v>5</v>
@@ -6629,7 +6630,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B7" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C7" s="4">
         <v>5</v>
@@ -6661,7 +6662,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B8" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C8" s="4">
         <v>5</v>
@@ -6693,7 +6694,7 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B9" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C9" s="4">
         <v>5</v>
@@ -6725,7 +6726,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B10" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C10" s="4">
         <v>5</v>
@@ -6757,7 +6758,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B11" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C11" s="4">
         <v>5</v>
@@ -6858,7 +6859,7 @@
   <sheetData>
     <row r="1" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E1"/>
       <c r="F1"/>
@@ -6869,12 +6870,12 @@
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B2" s="176" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C2" s="177"/>
       <c r="D2" s="145"/>
       <c r="E2" s="149" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F2" s="150"/>
       <c r="G2" s="150"/>
@@ -6884,42 +6885,42 @@
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B3" s="134" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C3" s="81" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D3" s="130" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E3" s="82" t="s">
+        <v>192</v>
+      </c>
+      <c r="F3" s="82" t="s">
         <v>193</v>
       </c>
-      <c r="F3" s="82" t="s">
+      <c r="G3" s="82" t="s">
         <v>194</v>
       </c>
-      <c r="G3" s="82" t="s">
+      <c r="H3" s="82" t="s">
         <v>195</v>
       </c>
-      <c r="H3" s="82" t="s">
+      <c r="I3" s="82" t="s">
         <v>196</v>
       </c>
-      <c r="I3" s="82" t="s">
+      <c r="J3" s="82" t="s">
         <v>197</v>
-      </c>
-      <c r="J3" s="82" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B4" s="103" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D4" s="125" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E4" s="77" t="s">
         <v>2</v>
@@ -6942,10 +6943,10 @@
     </row>
     <row r="5" spans="2:10" hidden="1" x14ac:dyDescent="0.4">
       <c r="B5" s="28" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D5">
         <v>6</v>
@@ -6971,10 +6972,10 @@
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B6" s="28" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C6" s="131" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D6" s="28">
         <v>6</v>
@@ -7000,10 +7001,10 @@
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B7" s="28" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C7" s="131" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D7" s="28">
         <v>6</v>
@@ -7029,10 +7030,10 @@
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B8" s="28" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C8" s="132" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D8" s="28">
         <v>6</v>
@@ -7058,10 +7059,10 @@
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B9" s="28" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C9" s="133" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D9" s="28">
         <v>6</v>
@@ -7107,7 +7108,7 @@
   <sheetData>
     <row r="1" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="2" spans="2:4" x14ac:dyDescent="0.4">
@@ -7119,13 +7120,13 @@
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B3" s="103" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C3" s="103" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D3" s="103" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.4">
@@ -7136,84 +7137,84 @@
         <v>1</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B5" s="28" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B6" s="28" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B7" s="28" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C7" s="28" t="s">
         <v>35</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B8" s="28" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B9" s="28" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B10" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B11" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>289</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>290</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Datatable.xlsx
+++ b/Assets/Data/Datatable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\RPG\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0943BB64-DBEC-477A-B366-B734311B0F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65C4B982-959B-406F-B1C5-679FDA2419F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{1A0CE3EC-C9BF-49DF-A1BD-F2CBB20E8474}"/>
+    <workbookView xWindow="1440" yWindow="3120" windowWidth="13740" windowHeight="11295" firstSheet="5" activeTab="5" xr2:uid="{1A0CE3EC-C9BF-49DF-A1BD-F2CBB20E8474}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerData" sheetId="8" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="307">
   <si>
     <t>ID</t>
     <phoneticPr fontId="4"/>
@@ -1610,10 +1610,6 @@
     <t>gro000</t>
   </si>
   <si>
-    <t>cat7</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>ショップ</t>
     <phoneticPr fontId="4"/>
   </si>
@@ -1636,6 +1632,101 @@
   </si>
   <si>
     <t>arm002</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>cat007</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>cat008</t>
+  </si>
+  <si>
+    <t>クエスト</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>quest</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t xml:space="preserve">クエスト </t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>討伐</t>
+    <rPh sb="0" eb="2">
+      <t>トウバツ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>納品</t>
+    <rPh sb="0" eb="2">
+      <t>ノウヒン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>収集</t>
+    <rPh sb="0" eb="2">
+      <t>シュウシュウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>会話・訪問</t>
+    <rPh sb="0" eb="2">
+      <t>カイワ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ホウモン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>護衛</t>
+    <rPh sb="0" eb="2">
+      <t>ゴエイ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>防衛</t>
+    <rPh sb="0" eb="2">
+      <t>ボウエイ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>制作</t>
+    <rPh sb="0" eb="2">
+      <t>セイサク</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>使用</t>
+    <rPh sb="0" eb="2">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>行商</t>
+    <rPh sb="0" eb="2">
+      <t>ギョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>探索・到達</t>
+    <rPh sb="0" eb="2">
+      <t>タンサク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>トウタツ</t>
+    </rPh>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -2650,7 +2741,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="181">
+  <cellXfs count="182">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3086,6 +3177,69 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3098,69 +3252,6 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3193,6 +3284,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4096,31 +4190,31 @@
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A2" s="6"/>
-      <c r="B2" s="152" t="s">
+      <c r="B2" s="154" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="153"/>
-      <c r="D2" s="154"/>
-      <c r="E2" s="155" t="s">
+      <c r="C2" s="155"/>
+      <c r="D2" s="156"/>
+      <c r="E2" s="157" t="s">
         <v>228</v>
       </c>
-      <c r="F2" s="156"/>
-      <c r="G2" s="156"/>
-      <c r="H2" s="156"/>
-      <c r="I2" s="156"/>
-      <c r="J2" s="156"/>
-      <c r="K2" s="156"/>
-      <c r="L2" s="156"/>
-      <c r="M2" s="156"/>
-      <c r="N2" s="156"/>
-      <c r="O2" s="156"/>
-      <c r="P2" s="156"/>
-      <c r="Q2" s="149" t="s">
+      <c r="F2" s="158"/>
+      <c r="G2" s="158"/>
+      <c r="H2" s="158"/>
+      <c r="I2" s="158"/>
+      <c r="J2" s="158"/>
+      <c r="K2" s="158"/>
+      <c r="L2" s="158"/>
+      <c r="M2" s="158"/>
+      <c r="N2" s="158"/>
+      <c r="O2" s="158"/>
+      <c r="P2" s="158"/>
+      <c r="Q2" s="151" t="s">
         <v>229</v>
       </c>
-      <c r="R2" s="150"/>
-      <c r="S2" s="150"/>
-      <c r="T2" s="151"/>
+      <c r="R2" s="152"/>
+      <c r="S2" s="152"/>
+      <c r="T2" s="153"/>
       <c r="U2" s="83" t="s">
         <v>151</v>
       </c>
@@ -4414,7 +4508,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DCEB796-C441-442B-BADD-688D3443B9D3}">
-  <dimension ref="B1:B40"/>
+  <dimension ref="B1:B52"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="20.75" customWidth="1"/>
@@ -4593,6 +4687,61 @@
     <row r="40" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B40" s="28" t="s">
         <v>189</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B42" s="181" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B43" s="28" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B44" s="28" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B45" s="28" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B46" s="28" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B47" s="28" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B48" s="28" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B49" s="28" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B50" s="28" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B51" s="28" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B52" s="28" t="s">
+        <v>305</v>
       </c>
     </row>
   </sheetData>
@@ -4631,21 +4780,21 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A2" s="6"/>
-      <c r="B2" s="157" t="s">
+      <c r="B2" s="159" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="158"/>
-      <c r="D2" s="159"/>
-      <c r="E2" s="160" t="s">
+      <c r="C2" s="160"/>
+      <c r="D2" s="161"/>
+      <c r="E2" s="162" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="161"/>
-      <c r="G2" s="162"/>
-      <c r="H2" s="162"/>
-      <c r="I2" s="162"/>
-      <c r="J2" s="162"/>
-      <c r="K2" s="163"/>
-      <c r="L2" s="163"/>
+      <c r="F2" s="163"/>
+      <c r="G2" s="164"/>
+      <c r="H2" s="164"/>
+      <c r="I2" s="164"/>
+      <c r="J2" s="164"/>
+      <c r="K2" s="165"/>
+      <c r="L2" s="165"/>
       <c r="M2" s="90" t="s">
         <v>151</v>
       </c>
@@ -4959,17 +5108,17 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A2" s="33"/>
-      <c r="B2" s="167" t="s">
+      <c r="B2" s="148" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="168"/>
-      <c r="D2" s="169"/>
-      <c r="E2" s="164" t="s">
+      <c r="C2" s="149"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="F2" s="165"/>
-      <c r="G2" s="165"/>
-      <c r="H2" s="166"/>
+      <c r="F2" s="146"/>
+      <c r="G2" s="146"/>
+      <c r="H2" s="147"/>
       <c r="I2" s="34"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.4">
@@ -5275,22 +5424,22 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2" s="33"/>
-      <c r="B2" s="145" t="s">
+      <c r="B2" s="166" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="145"/>
-      <c r="D2" s="146"/>
+      <c r="C2" s="166"/>
+      <c r="D2" s="167"/>
       <c r="E2" s="72" t="s">
         <v>159</v>
       </c>
-      <c r="F2" s="147" t="s">
+      <c r="F2" s="168" t="s">
         <v>49</v>
       </c>
-      <c r="G2" s="147"/>
-      <c r="H2" s="148"/>
-      <c r="I2" s="148"/>
-      <c r="J2" s="148"/>
-      <c r="K2" s="148"/>
+      <c r="G2" s="168"/>
+      <c r="H2" s="169"/>
+      <c r="I2" s="169"/>
+      <c r="J2" s="169"/>
+      <c r="K2" s="169"/>
       <c r="L2" s="34"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.4">
@@ -5553,13 +5702,13 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B11" s="28" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C11" s="28">
         <v>3</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E11" s="41" t="s">
         <v>46</v>
@@ -5738,17 +5887,17 @@
       <c r="E2" s="72" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="147" t="s">
+      <c r="F2" s="168" t="s">
         <v>49</v>
       </c>
-      <c r="G2" s="147"/>
-      <c r="H2" s="147"/>
-      <c r="I2" s="147"/>
-      <c r="J2" s="147"/>
-      <c r="K2" s="147"/>
-      <c r="L2" s="147"/>
-      <c r="M2" s="147"/>
-      <c r="N2" s="148"/>
+      <c r="G2" s="168"/>
+      <c r="H2" s="168"/>
+      <c r="I2" s="168"/>
+      <c r="J2" s="168"/>
+      <c r="K2" s="168"/>
+      <c r="L2" s="168"/>
+      <c r="M2" s="168"/>
+      <c r="N2" s="169"/>
       <c r="O2" s="5"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.4">
@@ -5995,7 +6144,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.4">
       <c r="B9" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C9" s="3">
         <v>3</v>
@@ -6485,15 +6634,15 @@
       </c>
       <c r="C2" s="170"/>
       <c r="D2" s="171"/>
-      <c r="E2" s="164" t="s">
+      <c r="E2" s="145" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="165"/>
-      <c r="G2" s="165"/>
-      <c r="H2" s="165"/>
-      <c r="I2" s="165"/>
-      <c r="J2" s="165"/>
-      <c r="K2" s="166"/>
+      <c r="F2" s="146"/>
+      <c r="G2" s="146"/>
+      <c r="H2" s="146"/>
+      <c r="I2" s="146"/>
+      <c r="J2" s="146"/>
+      <c r="K2" s="147"/>
       <c r="L2" s="5"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.4">
@@ -6873,15 +7022,15 @@
         <v>190</v>
       </c>
       <c r="C2" s="177"/>
-      <c r="D2" s="145"/>
-      <c r="E2" s="149" t="s">
+      <c r="D2" s="166"/>
+      <c r="E2" s="151" t="s">
         <v>198</v>
       </c>
-      <c r="F2" s="150"/>
-      <c r="G2" s="150"/>
-      <c r="H2" s="150"/>
-      <c r="I2" s="150"/>
-      <c r="J2" s="150"/>
+      <c r="F2" s="152"/>
+      <c r="G2" s="152"/>
+      <c r="H2" s="152"/>
+      <c r="I2" s="152"/>
+      <c r="J2" s="152"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B3" s="134" t="s">
@@ -7099,7 +7248,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAA933DC-85D5-45A0-AB5E-C05325866C50}">
-  <dimension ref="B1:D11"/>
+  <dimension ref="B1:D12"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="18.125" customWidth="1"/>
@@ -7208,13 +7357,24 @@
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B11" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>289</v>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B12" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>295</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Datatable.xlsx
+++ b/Assets/Data/Datatable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\RPG\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65C4B982-959B-406F-B1C5-679FDA2419F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{484D7236-2EAC-4BB3-BA76-576184104DA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="3120" windowWidth="13740" windowHeight="11295" firstSheet="5" activeTab="5" xr2:uid="{1A0CE3EC-C9BF-49DF-A1BD-F2CBB20E8474}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="4" xr2:uid="{1A0CE3EC-C9BF-49DF-A1BD-F2CBB20E8474}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerData" sheetId="8" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="317">
   <si>
     <t>ID</t>
     <phoneticPr fontId="4"/>
@@ -1727,6 +1727,78 @@
     <rPh sb="3" eb="5">
       <t>トウタツ</t>
     </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>木でできた棒</t>
+    <rPh sb="0" eb="1">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ボウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>防具_頭</t>
+    <rPh sb="0" eb="2">
+      <t>ボウグ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>アタマ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>防具_体</t>
+    <rPh sb="0" eb="2">
+      <t>ボウグ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カラダ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>防具_腰</t>
+    <rPh sb="0" eb="2">
+      <t>ボウグ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>コシ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>防具_足</t>
+    <rPh sb="0" eb="2">
+      <t>ボウグ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>アシ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>arm004</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>arm005</t>
+  </si>
+  <si>
+    <t>ゴルドーレギンス</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ボロボロの靴</t>
+    <rPh sb="5" eb="6">
+      <t>クツ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ゴルドーのレギンス</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -1923,7 +1995,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="67">
+  <borders count="65">
     <border>
       <left/>
       <right/>
@@ -2250,34 +2322,6 @@
       </right>
       <top style="double">
         <color theme="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="double">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="double">
-        <color indexed="64"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -2741,7 +2785,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="182">
+  <cellXfs count="179">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2916,39 +2960,24 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="38" fontId="0" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="6" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="0" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="0" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="6" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="0" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="0" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="0" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2973,79 +3002,79 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3066,22 +3095,22 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1">
@@ -3108,19 +3137,19 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
@@ -3132,161 +3161,167 @@
     <xf numFmtId="176" fontId="0" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="5" fillId="2" borderId="58" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1">
+    <xf numFmtId="38" fontId="0" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="5" fillId="2" borderId="60" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="38" fontId="0" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="38" fontId="0" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="61" xfId="2" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="38" fontId="0" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="63" xfId="2" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="38" fontId="5" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3294,7 +3329,7 @@
     <cellStyle name="桁区切り" xfId="1" builtinId="6"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="26">
+  <dxfs count="32">
     <dxf>
       <fill>
         <patternFill>
@@ -3350,6 +3385,48 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFCC99FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4190,157 +4267,157 @@
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A2" s="6"/>
-      <c r="B2" s="154" t="s">
+      <c r="B2" s="150" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="155"/>
-      <c r="D2" s="156"/>
-      <c r="E2" s="157" t="s">
+      <c r="C2" s="151"/>
+      <c r="D2" s="152"/>
+      <c r="E2" s="153" t="s">
         <v>228</v>
       </c>
-      <c r="F2" s="158"/>
-      <c r="G2" s="158"/>
-      <c r="H2" s="158"/>
-      <c r="I2" s="158"/>
-      <c r="J2" s="158"/>
-      <c r="K2" s="158"/>
-      <c r="L2" s="158"/>
-      <c r="M2" s="158"/>
-      <c r="N2" s="158"/>
-      <c r="O2" s="158"/>
-      <c r="P2" s="158"/>
-      <c r="Q2" s="151" t="s">
+      <c r="F2" s="154"/>
+      <c r="G2" s="154"/>
+      <c r="H2" s="154"/>
+      <c r="I2" s="154"/>
+      <c r="J2" s="154"/>
+      <c r="K2" s="154"/>
+      <c r="L2" s="154"/>
+      <c r="M2" s="154"/>
+      <c r="N2" s="154"/>
+      <c r="O2" s="154"/>
+      <c r="P2" s="154"/>
+      <c r="Q2" s="147" t="s">
         <v>229</v>
       </c>
-      <c r="R2" s="152"/>
-      <c r="S2" s="152"/>
-      <c r="T2" s="153"/>
-      <c r="U2" s="83" t="s">
+      <c r="R2" s="148"/>
+      <c r="S2" s="148"/>
+      <c r="T2" s="149"/>
+      <c r="U2" s="78" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="B3" s="81" t="s">
+      <c r="B3" s="76" t="s">
         <v>131</v>
       </c>
-      <c r="C3" s="81" t="s">
+      <c r="C3" s="76" t="s">
         <v>232</v>
       </c>
-      <c r="D3" s="81" t="s">
+      <c r="D3" s="76" t="s">
         <v>133</v>
       </c>
-      <c r="E3" s="82" t="s">
+      <c r="E3" s="77" t="s">
         <v>206</v>
       </c>
-      <c r="F3" s="82" t="s">
+      <c r="F3" s="77" t="s">
         <v>136</v>
       </c>
-      <c r="G3" s="82" t="s">
+      <c r="G3" s="77" t="s">
         <v>209</v>
       </c>
-      <c r="H3" s="82" t="s">
+      <c r="H3" s="77" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="82" t="s">
+      <c r="I3" s="77" t="s">
         <v>212</v>
       </c>
-      <c r="J3" s="82" t="s">
+      <c r="J3" s="77" t="s">
         <v>213</v>
       </c>
-      <c r="K3" s="82" t="s">
+      <c r="K3" s="77" t="s">
         <v>216</v>
       </c>
-      <c r="L3" s="82" t="s">
+      <c r="L3" s="77" t="s">
         <v>219</v>
       </c>
-      <c r="M3" s="82" t="s">
+      <c r="M3" s="77" t="s">
         <v>221</v>
       </c>
-      <c r="N3" s="82" t="s">
+      <c r="N3" s="77" t="s">
         <v>223</v>
       </c>
-      <c r="O3" s="82" t="s">
+      <c r="O3" s="77" t="s">
         <v>224</v>
       </c>
-      <c r="P3" s="82" t="s">
+      <c r="P3" s="77" t="s">
         <v>227</v>
       </c>
-      <c r="Q3" s="82" t="s">
+      <c r="Q3" s="77" t="s">
         <v>144</v>
       </c>
-      <c r="R3" s="84" t="s">
+      <c r="R3" s="79" t="s">
         <v>204</v>
       </c>
-      <c r="S3" s="84" t="s">
+      <c r="S3" s="79" t="s">
         <v>182</v>
       </c>
       <c r="T3" s="25" t="s">
         <v>184</v>
       </c>
-      <c r="U3" s="85" t="s">
+      <c r="U3" s="80" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A4" s="6"/>
-      <c r="B4" s="78" t="s">
+      <c r="B4" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="124" t="s">
+      <c r="C4" s="119" t="s">
         <v>231</v>
       </c>
       <c r="D4" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="77" t="s">
+      <c r="E4" s="72" t="s">
         <v>207</v>
       </c>
-      <c r="F4" s="77" t="s">
+      <c r="F4" s="72" t="s">
         <v>208</v>
       </c>
-      <c r="G4" s="77" t="s">
+      <c r="G4" s="72" t="s">
         <v>210</v>
       </c>
-      <c r="H4" s="77" t="s">
+      <c r="H4" s="72" t="s">
         <v>211</v>
       </c>
-      <c r="I4" s="79" t="s">
+      <c r="I4" s="74" t="s">
         <v>214</v>
       </c>
-      <c r="J4" s="79" t="s">
+      <c r="J4" s="74" t="s">
         <v>215</v>
       </c>
-      <c r="K4" s="80" t="s">
+      <c r="K4" s="75" t="s">
         <v>217</v>
       </c>
-      <c r="L4" s="80" t="s">
+      <c r="L4" s="75" t="s">
         <v>218</v>
       </c>
-      <c r="M4" s="79" t="s">
+      <c r="M4" s="74" t="s">
         <v>220</v>
       </c>
-      <c r="N4" s="79" t="s">
+      <c r="N4" s="74" t="s">
         <v>222</v>
       </c>
-      <c r="O4" s="79" t="s">
+      <c r="O4" s="74" t="s">
         <v>225</v>
       </c>
-      <c r="P4" s="79" t="s">
+      <c r="P4" s="74" t="s">
         <v>226</v>
       </c>
-      <c r="Q4" s="109" t="s">
+      <c r="Q4" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="R4" s="108" t="s">
+      <c r="R4" s="103" t="s">
         <v>205</v>
       </c>
-      <c r="S4" s="108" t="s">
+      <c r="S4" s="103" t="s">
         <v>183</v>
       </c>
-      <c r="T4" s="110" t="s">
+      <c r="T4" s="105" t="s">
         <v>185</v>
       </c>
-      <c r="U4" s="85" t="s">
+      <c r="U4" s="80" t="s">
         <v>140</v>
       </c>
     </row>
@@ -4393,16 +4470,16 @@
       <c r="Q5" s="3">
         <v>10</v>
       </c>
-      <c r="R5" s="112">
+      <c r="R5" s="107">
         <v>100</v>
       </c>
-      <c r="S5" s="112">
+      <c r="S5" s="107">
         <v>99</v>
       </c>
       <c r="T5" s="41" t="s">
         <v>189</v>
       </c>
-      <c r="U5" s="113" t="s">
+      <c r="U5" s="108" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4496,7 +4573,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4CB99A45-EA7E-417D-BCBA-7EF9EF9D29A0}">
           <x14:formula1>
-            <xm:f>CategoryList!$B$37:$B$40</xm:f>
+            <xm:f>CategoryList!$B$40:$B$43</xm:f>
           </x14:formula1>
           <xm:sqref>T5:T1048576</xm:sqref>
         </x14:dataValidation>
@@ -4508,7 +4585,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DCEB796-C441-442B-BADD-688D3443B9D3}">
-  <dimension ref="B1:B52"/>
+  <dimension ref="B1:B55"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="20.75" customWidth="1"/>
@@ -4566,181 +4643,196 @@
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B12" s="28" t="s">
-        <v>37</v>
+        <v>308</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B13" s="28" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B14" s="29" t="s">
-        <v>115</v>
+      <c r="B14" s="28" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B15" s="28" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B16" s="28" t="s">
-        <v>58</v>
+        <v>311</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B17" s="28" t="s">
-        <v>230</v>
+      <c r="B17" s="29" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B18" s="28" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B19" s="28" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B20" s="28" t="s">
-        <v>59</v>
+        <v>230</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B21" s="28" t="s">
-        <v>46</v>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B22" s="28" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B23" s="29" t="s">
-        <v>55</v>
+      <c r="B23" s="28" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B24" s="28" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B25" s="28" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B26" s="28" t="s">
-        <v>66</v>
+      <c r="B26" s="29" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B27" s="28" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B28" s="28" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B29" s="28" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B30" s="28" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B31" s="28" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B30" s="70" t="s">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B33" s="65" t="s">
         <v>116</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B31" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B32" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B33" s="3" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B34" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B35" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B36" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B37" s="3" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B36" s="111" t="s">
+    <row r="39" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B39" s="106" t="s">
         <v>185</v>
-      </c>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B37" s="28" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B38" s="28" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B39" s="28" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="40" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B40" s="28" t="s">
-        <v>189</v>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B41" s="28" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="42" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B42" s="181" t="s">
-        <v>296</v>
+      <c r="B42" s="28" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="43" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B43" s="28" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B44" s="28" t="s">
-        <v>298</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B45" s="28" t="s">
-        <v>299</v>
+      <c r="B45" s="140" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="46" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B46" s="28" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="47" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B47" s="28" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="48" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B48" s="28" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B49" s="28" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
     </row>
     <row r="50" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B50" s="28" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="51" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B51" s="28" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="52" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B52" s="28" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B53" s="28" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B54" s="28" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B55" s="28" t="s">
         <v>305</v>
       </c>
     </row>
@@ -4780,61 +4872,61 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A2" s="6"/>
-      <c r="B2" s="159" t="s">
+      <c r="B2" s="155" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="160"/>
-      <c r="D2" s="161"/>
-      <c r="E2" s="162" t="s">
+      <c r="C2" s="156"/>
+      <c r="D2" s="157"/>
+      <c r="E2" s="158" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="163"/>
-      <c r="G2" s="164"/>
-      <c r="H2" s="164"/>
-      <c r="I2" s="164"/>
-      <c r="J2" s="164"/>
-      <c r="K2" s="165"/>
-      <c r="L2" s="165"/>
-      <c r="M2" s="90" t="s">
+      <c r="F2" s="159"/>
+      <c r="G2" s="160"/>
+      <c r="H2" s="160"/>
+      <c r="I2" s="160"/>
+      <c r="J2" s="160"/>
+      <c r="K2" s="161"/>
+      <c r="L2" s="161"/>
+      <c r="M2" s="85" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A3" s="6"/>
-      <c r="B3" s="86" t="s">
+      <c r="B3" s="81" t="s">
         <v>130</v>
       </c>
-      <c r="C3" s="87" t="s">
+      <c r="C3" s="82" t="s">
         <v>232</v>
       </c>
-      <c r="D3" s="87" t="s">
+      <c r="D3" s="82" t="s">
         <v>132</v>
       </c>
-      <c r="E3" s="88" t="s">
+      <c r="E3" s="83" t="s">
         <v>135</v>
       </c>
-      <c r="F3" s="88" t="s">
+      <c r="F3" s="83" t="s">
         <v>137</v>
       </c>
-      <c r="G3" s="88" t="s">
+      <c r="G3" s="83" t="s">
         <v>134</v>
       </c>
-      <c r="H3" s="88" t="s">
+      <c r="H3" s="83" t="s">
         <v>147</v>
       </c>
-      <c r="I3" s="88" t="s">
+      <c r="I3" s="83" t="s">
         <v>149</v>
       </c>
-      <c r="J3" s="88" t="s">
+      <c r="J3" s="83" t="s">
         <v>145</v>
       </c>
-      <c r="K3" s="88" t="s">
+      <c r="K3" s="83" t="s">
         <v>152</v>
       </c>
-      <c r="L3" s="89" t="s">
+      <c r="L3" s="84" t="s">
         <v>143</v>
       </c>
-      <c r="M3" s="91" t="s">
+      <c r="M3" s="86" t="s">
         <v>141</v>
       </c>
     </row>
@@ -4843,7 +4935,7 @@
       <c r="B4" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="125" t="s">
+      <c r="C4" s="120" t="s">
         <v>231</v>
       </c>
       <c r="D4" s="24" t="s">
@@ -4873,7 +4965,7 @@
       <c r="L4" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="M4" s="83" t="s">
+      <c r="M4" s="78" t="s">
         <v>139</v>
       </c>
     </row>
@@ -5092,7 +5184,7 @@
     <col min="4" max="4" width="11.125" customWidth="1"/>
     <col min="5" max="5" width="13.25" customWidth="1"/>
     <col min="6" max="6" width="14.625" customWidth="1"/>
-    <col min="8" max="8" width="11.125" style="118" customWidth="1"/>
+    <col min="8" max="8" width="11.125" style="113" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.4">
@@ -5108,53 +5200,53 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A2" s="33"/>
-      <c r="B2" s="148" t="s">
+      <c r="B2" s="165" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="149"/>
-      <c r="D2" s="150"/>
-      <c r="E2" s="145" t="s">
+      <c r="C2" s="166"/>
+      <c r="D2" s="167"/>
+      <c r="E2" s="162" t="s">
         <v>35</v>
       </c>
-      <c r="F2" s="146"/>
-      <c r="G2" s="146"/>
-      <c r="H2" s="147"/>
+      <c r="F2" s="163"/>
+      <c r="G2" s="163"/>
+      <c r="H2" s="164"/>
       <c r="I2" s="34"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A3" s="33"/>
-      <c r="B3" s="95" t="s">
+      <c r="B3" s="90" t="s">
         <v>153</v>
       </c>
-      <c r="C3" s="74" t="s">
+      <c r="C3" s="69" t="s">
         <v>232</v>
       </c>
-      <c r="D3" s="74" t="s">
+      <c r="D3" s="69" t="s">
         <v>154</v>
       </c>
-      <c r="E3" s="92" t="s">
+      <c r="E3" s="87" t="s">
         <v>155</v>
       </c>
-      <c r="F3" s="93" t="s">
+      <c r="F3" s="88" t="s">
         <v>181</v>
       </c>
-      <c r="G3" s="93" t="s">
+      <c r="G3" s="88" t="s">
         <v>156</v>
       </c>
-      <c r="H3" s="94" t="s">
+      <c r="H3" s="89" t="s">
         <v>157</v>
       </c>
       <c r="I3" s="34"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4" s="33"/>
-      <c r="B4" s="74" t="s">
+      <c r="B4" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="74" t="s">
+      <c r="C4" s="69" t="s">
         <v>233</v>
       </c>
-      <c r="D4" s="123" t="s">
+      <c r="D4" s="118" t="s">
         <v>28</v>
       </c>
       <c r="E4" s="31" t="s">
@@ -5190,55 +5282,55 @@
       <c r="G5" s="28">
         <v>1</v>
       </c>
-      <c r="H5" s="115">
+      <c r="H5" s="110">
         <v>0.2</v>
       </c>
       <c r="I5" s="34"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="B6" s="128" t="s">
+      <c r="B6" s="123" t="s">
         <v>240</v>
       </c>
-      <c r="C6" s="128">
+      <c r="C6" s="123">
         <v>2</v>
       </c>
-      <c r="D6" s="128" t="s">
+      <c r="D6" s="123" t="s">
         <v>234</v>
       </c>
-      <c r="E6" s="128" t="s">
+      <c r="E6" s="123" t="s">
         <v>251</v>
       </c>
-      <c r="F6" s="128" t="s">
+      <c r="F6" s="123" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="128">
+      <c r="G6" s="123">
         <v>1</v>
       </c>
-      <c r="H6" s="129">
+      <c r="H6" s="124">
         <v>0.2</v>
       </c>
       <c r="I6" s="34"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="B7" s="128" t="s">
+      <c r="B7" s="123" t="s">
         <v>241</v>
       </c>
-      <c r="C7" s="128">
+      <c r="C7" s="123">
         <v>2</v>
       </c>
-      <c r="D7" s="128" t="s">
+      <c r="D7" s="123" t="s">
         <v>234</v>
       </c>
-      <c r="E7" s="128" t="s">
+      <c r="E7" s="123" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="128" t="s">
+      <c r="F7" s="123" t="s">
         <v>40</v>
       </c>
-      <c r="G7" s="128">
+      <c r="G7" s="123">
         <v>1</v>
       </c>
-      <c r="H7" s="129">
+      <c r="H7" s="124">
         <v>0.2</v>
       </c>
       <c r="I7" s="34"/>
@@ -5262,79 +5354,79 @@
       <c r="G8" s="28">
         <v>1</v>
       </c>
-      <c r="H8" s="115">
+      <c r="H8" s="110">
         <v>1</v>
       </c>
       <c r="I8" s="34"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="B9" s="128" t="s">
+      <c r="B9" s="123" t="s">
         <v>243</v>
       </c>
-      <c r="C9" s="128">
+      <c r="C9" s="123">
         <v>2</v>
       </c>
-      <c r="D9" s="128" t="s">
+      <c r="D9" s="123" t="s">
         <v>248</v>
       </c>
-      <c r="E9" s="128" t="s">
+      <c r="E9" s="123" t="s">
         <v>34</v>
       </c>
-      <c r="F9" s="128" t="s">
+      <c r="F9" s="123" t="s">
         <v>41</v>
       </c>
-      <c r="G9" s="128">
+      <c r="G9" s="123">
         <v>1</v>
       </c>
-      <c r="H9" s="129">
+      <c r="H9" s="124">
         <v>0.2</v>
       </c>
       <c r="I9" s="34"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="B10" s="128" t="s">
+      <c r="B10" s="123" t="s">
         <v>244</v>
       </c>
-      <c r="C10" s="128">
+      <c r="C10" s="123">
         <v>2</v>
       </c>
-      <c r="D10" s="128" t="s">
+      <c r="D10" s="123" t="s">
         <v>248</v>
       </c>
-      <c r="E10" s="128" t="s">
+      <c r="E10" s="123" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="128" t="s">
+      <c r="F10" s="123" t="s">
         <v>43</v>
       </c>
-      <c r="G10" s="128">
+      <c r="G10" s="123">
         <v>1</v>
       </c>
-      <c r="H10" s="129">
+      <c r="H10" s="124">
         <v>0.2</v>
       </c>
       <c r="I10" s="34"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="B11" s="128" t="s">
+      <c r="B11" s="123" t="s">
         <v>245</v>
       </c>
-      <c r="C11" s="128">
+      <c r="C11" s="123">
         <v>2</v>
       </c>
-      <c r="D11" s="128" t="s">
+      <c r="D11" s="123" t="s">
         <v>248</v>
       </c>
-      <c r="E11" s="128" t="s">
+      <c r="E11" s="123" t="s">
         <v>37</v>
       </c>
-      <c r="F11" s="128" t="s">
+      <c r="F11" s="123" t="s">
         <v>44</v>
       </c>
-      <c r="G11" s="128">
+      <c r="G11" s="123">
         <v>1</v>
       </c>
-      <c r="H11" s="129">
+      <c r="H11" s="124">
         <v>0.2</v>
       </c>
       <c r="I11" s="34"/>
@@ -5358,7 +5450,7 @@
       <c r="G12" s="28">
         <v>1</v>
       </c>
-      <c r="H12" s="115">
+      <c r="H12" s="110">
         <v>0.2</v>
       </c>
     </row>
@@ -5381,7 +5473,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4ECC273F-E5D2-4C34-949F-056CA74E409D}">
           <x14:formula1>
-            <xm:f>CategoryList!$B$8:$B$12</xm:f>
+            <xm:f>CategoryList!$B$8:$B$15</xm:f>
           </x14:formula1>
           <xm:sqref>E5:E1048576</xm:sqref>
         </x14:dataValidation>
@@ -5400,7 +5492,7 @@
     <col min="4" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="9" style="1"/>
     <col min="6" max="6" width="11.75" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.5" style="118" customWidth="1"/>
+    <col min="7" max="7" width="12.5" style="113" customWidth="1"/>
     <col min="8" max="8" width="13.375" style="52" customWidth="1"/>
     <col min="9" max="9" width="9" style="36"/>
     <col min="10" max="10" width="13.5" style="1" customWidth="1"/>
@@ -5424,54 +5516,54 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2" s="33"/>
-      <c r="B2" s="166" t="s">
+      <c r="B2" s="168" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="166"/>
-      <c r="D2" s="167"/>
-      <c r="E2" s="72" t="s">
+      <c r="C2" s="168"/>
+      <c r="D2" s="169"/>
+      <c r="E2" s="67" t="s">
         <v>159</v>
       </c>
-      <c r="F2" s="168" t="s">
+      <c r="F2" s="145" t="s">
         <v>49</v>
       </c>
-      <c r="G2" s="168"/>
-      <c r="H2" s="169"/>
-      <c r="I2" s="169"/>
-      <c r="J2" s="169"/>
-      <c r="K2" s="169"/>
+      <c r="G2" s="145"/>
+      <c r="H2" s="146"/>
+      <c r="I2" s="146"/>
+      <c r="J2" s="146"/>
+      <c r="K2" s="146"/>
       <c r="L2" s="34"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3" s="33"/>
-      <c r="B3" s="96" t="s">
+      <c r="B3" s="91" t="s">
         <v>153</v>
       </c>
-      <c r="C3" s="74" t="s">
+      <c r="C3" s="69" t="s">
         <v>232</v>
       </c>
-      <c r="D3" s="97" t="s">
+      <c r="D3" s="92" t="s">
         <v>160</v>
       </c>
-      <c r="E3" s="93" t="s">
+      <c r="E3" s="88" t="s">
         <v>155</v>
       </c>
-      <c r="F3" s="79" t="s">
+      <c r="F3" s="74" t="s">
         <v>162</v>
       </c>
-      <c r="G3" s="79" t="s">
+      <c r="G3" s="74" t="s">
         <v>163</v>
       </c>
-      <c r="H3" s="98" t="s">
+      <c r="H3" s="93" t="s">
         <v>164</v>
       </c>
-      <c r="I3" s="98" t="s">
+      <c r="I3" s="93" t="s">
         <v>165</v>
       </c>
-      <c r="J3" s="79" t="s">
+      <c r="J3" s="74" t="s">
         <v>142</v>
       </c>
-      <c r="K3" s="98" t="s">
+      <c r="K3" s="93" t="s">
         <v>166</v>
       </c>
       <c r="L3" s="34"/>
@@ -5481,7 +5573,7 @@
       <c r="B4" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="74" t="s">
+      <c r="C4" s="69" t="s">
         <v>233</v>
       </c>
       <c r="D4" s="37" t="s">
@@ -5526,7 +5618,7 @@
       <c r="F5" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="G5" s="114">
+      <c r="G5" s="109">
         <v>1.25</v>
       </c>
       <c r="H5" s="48" t="s">
@@ -5535,7 +5627,7 @@
       <c r="I5" s="55">
         <v>499</v>
       </c>
-      <c r="J5" s="143"/>
+      <c r="J5" s="138"/>
       <c r="K5" s="45" t="s">
         <v>203</v>
       </c>
@@ -5556,19 +5648,19 @@
       <c r="F6" s="46" t="s">
         <v>230</v>
       </c>
-      <c r="G6" s="114">
+      <c r="G6" s="109">
         <v>1</v>
       </c>
       <c r="H6" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="I6" s="135">
+      <c r="I6" s="130">
         <v>500</v>
       </c>
       <c r="J6" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="K6" s="139" t="s">
+      <c r="K6" s="134" t="s">
         <v>78</v>
       </c>
     </row>
@@ -5588,19 +5680,19 @@
       <c r="F7" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="G7" s="115">
+      <c r="G7" s="110">
         <v>0.5</v>
       </c>
       <c r="H7" s="49" t="s">
         <v>63</v>
       </c>
-      <c r="I7" s="136">
+      <c r="I7" s="131">
         <v>300</v>
       </c>
       <c r="J7" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="K7" s="140" t="s">
+      <c r="K7" s="135" t="s">
         <v>80</v>
       </c>
     </row>
@@ -5620,19 +5712,19 @@
       <c r="F8" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="G8" s="116">
+      <c r="G8" s="111">
         <v>0</v>
       </c>
       <c r="H8" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="I8" s="137">
+      <c r="I8" s="132">
         <v>10</v>
       </c>
-      <c r="J8" s="144" t="s">
+      <c r="J8" s="139" t="s">
         <v>17</v>
       </c>
-      <c r="K8" s="141" t="s">
+      <c r="K8" s="136" t="s">
         <v>79</v>
       </c>
     </row>
@@ -5652,19 +5744,19 @@
       <c r="F9" s="43" t="s">
         <v>46</v>
       </c>
-      <c r="G9" s="117">
+      <c r="G9" s="112">
         <v>0</v>
       </c>
       <c r="H9" s="51" t="s">
         <v>69</v>
       </c>
-      <c r="I9" s="138">
+      <c r="I9" s="133">
         <v>100000</v>
       </c>
       <c r="J9" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="K9" s="142" t="s">
+      <c r="K9" s="137" t="s">
         <v>84</v>
       </c>
     </row>
@@ -5684,19 +5776,19 @@
       <c r="F10" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="115">
+      <c r="G10" s="110">
         <v>0</v>
       </c>
       <c r="H10" s="49" t="s">
         <v>63</v>
       </c>
-      <c r="I10" s="136">
+      <c r="I10" s="131">
         <v>100</v>
       </c>
       <c r="J10" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="K10" s="140" t="s">
+      <c r="K10" s="135" t="s">
         <v>83</v>
       </c>
     </row>
@@ -5716,19 +5808,19 @@
       <c r="F11" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="G11" s="115">
+      <c r="G11" s="110">
         <v>0</v>
       </c>
       <c r="H11" s="49" t="s">
         <v>63</v>
       </c>
-      <c r="I11" s="136">
+      <c r="I11" s="131">
         <v>1000</v>
       </c>
       <c r="J11" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="140" t="s">
+      <c r="K11" s="135" t="s">
         <v>83</v>
       </c>
     </row>
@@ -5815,19 +5907,19 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C4E11946-AD91-4E30-B234-C540E1E6B80A}">
           <x14:formula1>
-            <xm:f>CategoryList!$B$8:$B$12</xm:f>
+            <xm:f>CategoryList!$B$8:$B$15</xm:f>
           </x14:formula1>
           <xm:sqref>E5:E1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3AA81EF7-93AC-4709-9E34-C0F696573A9F}">
           <x14:formula1>
-            <xm:f>CategoryList!$B$15:$B$21</xm:f>
+            <xm:f>CategoryList!$B$18:$B$24</xm:f>
           </x14:formula1>
           <xm:sqref>F5:F1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{703C6BAA-DA7A-423F-AD0C-00379B92FD30}">
           <x14:formula1>
-            <xm:f>CategoryList!$B$24:$B$28</xm:f>
+            <xm:f>CategoryList!$B$27:$B$31</xm:f>
           </x14:formula1>
           <xm:sqref>H5:H1048576</xm:sqref>
         </x14:dataValidation>
@@ -5845,11 +5937,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0252C608-E66C-4AFD-BC4B-F4AA87ED315A}">
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="12.625" customWidth="1"/>
-    <col min="4" max="4" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="14.875" customWidth="1"/>
     <col min="6" max="6" width="10.375" customWidth="1"/>
     <col min="7" max="7" width="12.125" customWidth="1"/>
@@ -5872,73 +5964,73 @@
       <c r="H1" s="7"/>
       <c r="I1" s="7"/>
       <c r="J1" s="7"/>
-      <c r="K1" s="62"/>
+      <c r="K1" s="59"/>
       <c r="L1" s="7"/>
       <c r="M1" s="7"/>
       <c r="N1" s="7"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A2" s="6"/>
-      <c r="B2" s="170" t="s">
+      <c r="B2" s="143" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="170"/>
-      <c r="D2" s="171"/>
-      <c r="E2" s="72" t="s">
+      <c r="C2" s="143"/>
+      <c r="D2" s="144"/>
+      <c r="E2" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="168" t="s">
+      <c r="F2" s="145" t="s">
         <v>49</v>
       </c>
-      <c r="G2" s="168"/>
-      <c r="H2" s="168"/>
-      <c r="I2" s="168"/>
-      <c r="J2" s="168"/>
-      <c r="K2" s="168"/>
-      <c r="L2" s="168"/>
-      <c r="M2" s="168"/>
-      <c r="N2" s="169"/>
+      <c r="G2" s="145"/>
+      <c r="H2" s="145"/>
+      <c r="I2" s="145"/>
+      <c r="J2" s="145"/>
+      <c r="K2" s="145"/>
+      <c r="L2" s="145"/>
+      <c r="M2" s="145"/>
+      <c r="N2" s="146"/>
       <c r="O2" s="5"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A3" s="6"/>
-      <c r="B3" s="99" t="s">
+      <c r="B3" s="94" t="s">
         <v>153</v>
       </c>
-      <c r="C3" s="87" t="s">
+      <c r="C3" s="82" t="s">
         <v>232</v>
       </c>
-      <c r="D3" s="100" t="s">
+      <c r="D3" s="95" t="s">
         <v>160</v>
       </c>
-      <c r="E3" s="93" t="s">
+      <c r="E3" s="88" t="s">
         <v>155</v>
       </c>
-      <c r="F3" s="82" t="s">
+      <c r="F3" s="77" t="s">
         <v>134</v>
       </c>
-      <c r="G3" s="82" t="s">
+      <c r="G3" s="77" t="s">
         <v>148</v>
       </c>
-      <c r="H3" s="82" t="s">
+      <c r="H3" s="77" t="s">
         <v>150</v>
       </c>
-      <c r="I3" s="82" t="s">
+      <c r="I3" s="77" t="s">
         <v>146</v>
       </c>
-      <c r="J3" s="79" t="s">
+      <c r="J3" s="74" t="s">
         <v>167</v>
       </c>
-      <c r="K3" s="98" t="s">
+      <c r="K3" s="93" t="s">
         <v>165</v>
       </c>
-      <c r="L3" s="79" t="s">
+      <c r="L3" s="74" t="s">
         <v>168</v>
       </c>
-      <c r="M3" s="79" t="s">
+      <c r="M3" s="74" t="s">
         <v>164</v>
       </c>
-      <c r="N3" s="98" t="s">
+      <c r="N3" s="93" t="s">
         <v>166</v>
       </c>
       <c r="O3" s="5"/>
@@ -5948,7 +6040,7 @@
       <c r="B4" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="125" t="s">
+      <c r="C4" s="120" t="s">
         <v>231</v>
       </c>
       <c r="D4" s="57" t="s">
@@ -5972,7 +6064,7 @@
       <c r="J4" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="K4" s="63" t="s">
+      <c r="K4" s="60" t="s">
         <v>45</v>
       </c>
       <c r="L4" s="26" t="s">
@@ -5996,7 +6088,7 @@
       <c r="D5" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="18" t="s">
         <v>36</v>
       </c>
       <c r="F5" s="3">
@@ -6014,7 +6106,7 @@
       <c r="J5" s="3">
         <v>0</v>
       </c>
-      <c r="K5" s="64">
+      <c r="K5" s="61">
         <v>100</v>
       </c>
       <c r="L5" s="13" t="s">
@@ -6023,7 +6115,9 @@
       <c r="M5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="N5" s="3"/>
+      <c r="N5" s="3" t="s">
+        <v>307</v>
+      </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.4">
       <c r="B6" s="3" t="s">
@@ -6035,7 +6129,7 @@
       <c r="D6" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="18" t="s">
         <v>36</v>
       </c>
       <c r="F6" s="3">
@@ -6053,7 +6147,7 @@
       <c r="J6" s="3">
         <v>0</v>
       </c>
-      <c r="K6" s="64">
+      <c r="K6" s="61">
         <v>200</v>
       </c>
       <c r="L6" s="13" t="s">
@@ -6064,83 +6158,83 @@
       </c>
       <c r="N6" s="3"/>
     </row>
-    <row r="7" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
       <c r="B7" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="3">
         <v>3</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="3">
         <v>0</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="3">
         <v>0</v>
       </c>
-      <c r="H7" s="20">
+      <c r="H7" s="3">
         <v>100</v>
       </c>
-      <c r="I7" s="20">
+      <c r="I7" s="3">
         <v>100</v>
       </c>
-      <c r="J7" s="20">
+      <c r="J7" s="3">
         <v>-2</v>
       </c>
-      <c r="K7" s="65">
+      <c r="K7" s="61">
         <v>300</v>
       </c>
-      <c r="L7" s="21" t="s">
+      <c r="L7" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="M7" s="20" t="s">
+      <c r="M7" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="N7" s="20"/>
-    </row>
-    <row r="8" spans="1:15" ht="19.5" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="60" t="s">
+      <c r="N7" s="3"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="B8" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="60">
+      <c r="C8" s="3">
         <v>3</v>
       </c>
-      <c r="D8" s="60" t="s">
+      <c r="D8" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E8" s="60" t="s">
-        <v>37</v>
-      </c>
-      <c r="F8" s="60">
+      <c r="E8" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="F8" s="3">
         <v>5</v>
       </c>
-      <c r="G8" s="60">
+      <c r="G8" s="3">
         <v>5</v>
       </c>
-      <c r="H8" s="60">
+      <c r="H8" s="3">
         <v>5</v>
       </c>
-      <c r="I8" s="60">
+      <c r="I8" s="3">
         <v>5</v>
       </c>
-      <c r="J8" s="60">
+      <c r="J8" s="3">
         <v>5</v>
       </c>
-      <c r="K8" s="66">
+      <c r="K8" s="61">
         <v>10000</v>
       </c>
-      <c r="L8" s="61" t="s">
+      <c r="L8" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="M8" s="60" t="s">
+      <c r="M8" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="N8" s="60"/>
+      <c r="N8" s="3"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.4">
       <c r="B9" s="3" t="s">
@@ -6152,8 +6246,8 @@
       <c r="D9" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>37</v>
+      <c r="E9" s="9" t="s">
+        <v>309</v>
       </c>
       <c r="F9" s="3">
         <v>5</v>
@@ -6170,7 +6264,7 @@
       <c r="J9" s="3">
         <v>5</v>
       </c>
-      <c r="K9" s="64">
+      <c r="K9" s="61">
         <v>1</v>
       </c>
       <c r="L9" s="13" t="s">
@@ -6181,18 +6275,18 @@
       </c>
       <c r="N9" s="3"/>
     </row>
-    <row r="10" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B10" s="59" t="s">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="B10" s="58" t="s">
         <v>95</v>
       </c>
-      <c r="C10" s="59">
+      <c r="C10" s="3">
         <v>3</v>
       </c>
       <c r="D10" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="E10" s="20" t="s">
-        <v>37</v>
+      <c r="E10" s="141" t="s">
+        <v>309</v>
       </c>
       <c r="F10" s="20">
         <v>5</v>
@@ -6209,7 +6303,7 @@
       <c r="J10" s="20">
         <v>5</v>
       </c>
-      <c r="K10" s="65">
+      <c r="K10" s="62">
         <v>3</v>
       </c>
       <c r="L10" s="21" t="s">
@@ -6220,57 +6314,59 @@
       </c>
       <c r="N10" s="20"/>
     </row>
-    <row r="11" spans="1:15" ht="19.5" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="60" t="s">
-        <v>94</v>
-      </c>
-      <c r="C11" s="60">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="B11" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="C11" s="3">
         <v>3</v>
       </c>
-      <c r="D11" s="58" t="s">
+      <c r="D11" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="F11" s="20">
+        <v>5</v>
+      </c>
+      <c r="G11" s="20">
+        <v>5</v>
+      </c>
+      <c r="H11" s="20">
+        <v>5</v>
+      </c>
+      <c r="I11" s="20">
+        <v>5</v>
+      </c>
+      <c r="J11" s="20">
+        <v>5</v>
+      </c>
+      <c r="K11" s="62">
         <v>100</v>
       </c>
-      <c r="E11" s="58" t="s">
-        <v>50</v>
-      </c>
-      <c r="F11" s="58">
-        <v>40</v>
-      </c>
-      <c r="G11" s="58">
-        <v>100</v>
-      </c>
-      <c r="H11" s="58">
-        <v>5</v>
-      </c>
-      <c r="I11" s="58">
-        <v>-10</v>
-      </c>
-      <c r="J11" s="58">
-        <v>0</v>
-      </c>
-      <c r="K11" s="67">
-        <v>20</v>
-      </c>
-      <c r="L11" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="M11" s="58" t="s">
-        <v>65</v>
-      </c>
-      <c r="N11" s="58"/>
+      <c r="L11" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.4">
       <c r="B12" s="3" t="s">
-        <v>96</v>
+        <v>313</v>
       </c>
       <c r="C12" s="3">
         <v>3</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>50</v>
+        <v>315</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>311</v>
       </c>
       <c r="F12" s="3">
         <v>5</v>
@@ -6285,18 +6381,96 @@
         <v>5</v>
       </c>
       <c r="J12" s="3">
+        <v>5</v>
+      </c>
+      <c r="K12" s="61">
+        <v>3</v>
+      </c>
+      <c r="L12" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="B13" s="58" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13" s="3">
+        <v>3</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E13" s="142" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" s="3">
+        <v>40</v>
+      </c>
+      <c r="G13" s="3">
+        <v>100</v>
+      </c>
+      <c r="H13" s="3">
+        <v>5</v>
+      </c>
+      <c r="I13" s="3">
+        <v>-10</v>
+      </c>
+      <c r="J13" s="3">
         <v>0</v>
       </c>
-      <c r="K12" s="64">
+      <c r="K13" s="61">
+        <v>20</v>
+      </c>
+      <c r="L13" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="B14" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C14" s="3">
+        <v>3</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" s="3">
         <v>5</v>
       </c>
-      <c r="L12" s="13" t="s">
+      <c r="G14" s="3">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="61">
+        <v>5</v>
+      </c>
+      <c r="L14" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="M12" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="N12" s="3"/>
+      <c r="N14" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6310,7 +6484,70 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{8E54BEB9-BD53-4BEB-977F-CD3533EF5BD6}">
+          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{5EB8FAFE-4F00-4691-89AB-54C8BBE0BC5C}">
+            <xm:f>CategoryList!$B$10</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="9" tint="0.79998168889431442"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{A45A66FB-9DAF-42EA-A628-7FC46A58C753}">
+            <xm:f>CategoryList!$B$15</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="7" tint="0.79998168889431442"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="3" operator="equal" id="{1D009B4E-0EFD-4678-BC4C-7871D1B38093}">
+            <xm:f>CategoryList!$B$14</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="7" tint="0.79998168889431442"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="4" operator="equal" id="{C73B5F51-69B4-4A26-A72D-2E96963B964A}">
+            <xm:f>CategoryList!$B$12</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="7" tint="0.79998168889431442"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="5" operator="equal" id="{2DCD87F1-3391-44F1-A47A-0CF794A1D49A}">
+            <xm:f>CategoryList!$B$13</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="7" tint="0.79998168889431442"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="7" operator="equal" id="{23ABB9CC-812F-42B8-A6B0-0B737E64154E}">
+            <xm:f>CategoryList!$B$11</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="8" tint="0.79998168889431442"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>E5:E1048576</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="10" operator="equal" id="{8E54BEB9-BD53-4BEB-977F-CD3533EF5BD6}">
             <xm:f>Magic_Attribute_Table!$D$11</xm:f>
             <x14:dxf>
               <fill>
@@ -6320,7 +6557,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{6BA2AC1B-CF18-4360-8DE3-E0F6947FD788}">
+          <x14:cfRule type="cellIs" priority="11" operator="equal" id="{6BA2AC1B-CF18-4360-8DE3-E0F6947FD788}">
             <xm:f>Magic_Attribute_Table!$D$10</xm:f>
             <x14:dxf>
               <fill>
@@ -6331,7 +6568,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="3" operator="equal" id="{983171FE-EE20-4F52-ADBC-7D6D9BF33DAE}">
+          <x14:cfRule type="cellIs" priority="12" operator="equal" id="{983171FE-EE20-4F52-ADBC-7D6D9BF33DAE}">
             <xm:f>Magic_Attribute_Table!$D$9</xm:f>
             <x14:dxf>
               <fill>
@@ -6341,7 +6578,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="4" operator="equal" id="{2BB710E3-2FCF-463A-BEB6-920FF80306F2}">
+          <x14:cfRule type="cellIs" priority="13" operator="equal" id="{2BB710E3-2FCF-463A-BEB6-920FF80306F2}">
             <xm:f>Magic_Attribute_Table!$D$8</xm:f>
             <x14:dxf>
               <fill>
@@ -6351,7 +6588,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="5" operator="equal" id="{112A2E9A-6C77-45BE-92C7-B4F5FD637FE9}">
+          <x14:cfRule type="cellIs" priority="14" operator="equal" id="{112A2E9A-6C77-45BE-92C7-B4F5FD637FE9}">
             <xm:f>Magic_Attribute_Table!$D$7</xm:f>
             <x14:dxf>
               <fill>
@@ -6361,7 +6598,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="6" operator="equal" id="{F2DE84CC-5E69-4239-B5CC-3A0EF74A75F4}">
+          <x14:cfRule type="cellIs" priority="15" operator="equal" id="{F2DE84CC-5E69-4239-B5CC-3A0EF74A75F4}">
             <xm:f>Magic_Attribute_Table!$D$6</xm:f>
             <x14:dxf>
               <fill>
@@ -6380,13 +6617,13 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{458C7E23-AC7E-4C68-84CE-CE0FE002D093}">
           <x14:formula1>
-            <xm:f>CategoryList!$B$8:$B$12</xm:f>
+            <xm:f>CategoryList!$B$8:$B$15</xm:f>
           </x14:formula1>
           <xm:sqref>E5:E1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{83D9E4FB-47E5-4559-8FB8-E789A610F549}">
           <x14:formula1>
-            <xm:f>CategoryList!$B$24:$B$28</xm:f>
+            <xm:f>CategoryList!$B$27:$B$31</xm:f>
           </x14:formula1>
           <xm:sqref>M5:M1048576</xm:sqref>
         </x14:dataValidation>
@@ -6433,88 +6670,88 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2" s="6"/>
-      <c r="B2" s="174" t="s">
+      <c r="B2" s="172" t="s">
         <v>108</v>
       </c>
-      <c r="C2" s="174"/>
-      <c r="D2" s="175"/>
-      <c r="E2" s="172" t="s">
+      <c r="C2" s="172"/>
+      <c r="D2" s="173"/>
+      <c r="E2" s="170" t="s">
         <v>109</v>
       </c>
-      <c r="F2" s="173"/>
-      <c r="G2" s="173"/>
-      <c r="H2" s="173"/>
-      <c r="I2" s="173"/>
-      <c r="J2" s="173"/>
-      <c r="K2" s="173"/>
+      <c r="F2" s="171"/>
+      <c r="G2" s="171"/>
+      <c r="H2" s="171"/>
+      <c r="I2" s="171"/>
+      <c r="J2" s="171"/>
+      <c r="K2" s="171"/>
       <c r="L2" s="5"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="B3" s="102" t="s">
+      <c r="B3" s="97" t="s">
         <v>153</v>
       </c>
-      <c r="C3" s="87" t="s">
+      <c r="C3" s="82" t="s">
         <v>232</v>
       </c>
-      <c r="D3" s="103" t="s">
+      <c r="D3" s="98" t="s">
         <v>160</v>
       </c>
-      <c r="E3" s="104" t="s">
+      <c r="E3" s="99" t="s">
         <v>171</v>
       </c>
-      <c r="F3" s="104" t="s">
+      <c r="F3" s="99" t="s">
         <v>161</v>
       </c>
-      <c r="G3" s="104" t="s">
+      <c r="G3" s="99" t="s">
         <v>163</v>
       </c>
-      <c r="H3" s="104" t="s">
+      <c r="H3" s="99" t="s">
         <v>172</v>
       </c>
-      <c r="I3" s="104" t="s">
+      <c r="I3" s="99" t="s">
         <v>164</v>
       </c>
-      <c r="J3" s="104" t="s">
+      <c r="J3" s="99" t="s">
         <v>173</v>
       </c>
-      <c r="K3" s="121" t="s">
+      <c r="K3" s="116" t="s">
         <v>166</v>
       </c>
-      <c r="L3" s="122"/>
+      <c r="L3" s="117"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4" s="6"/>
-      <c r="B4" s="69" t="s">
+      <c r="B4" s="64" t="s">
         <v>102</v>
       </c>
-      <c r="C4" s="125" t="s">
+      <c r="C4" s="120" t="s">
         <v>231</v>
       </c>
-      <c r="D4" s="101" t="s">
+      <c r="D4" s="96" t="s">
         <v>103</v>
       </c>
-      <c r="E4" s="79" t="s">
+      <c r="E4" s="74" t="s">
         <v>104</v>
       </c>
-      <c r="F4" s="80" t="s">
+      <c r="F4" s="75" t="s">
         <v>56</v>
       </c>
-      <c r="G4" s="79" t="s">
+      <c r="G4" s="74" t="s">
         <v>77</v>
       </c>
-      <c r="H4" s="80" t="s">
+      <c r="H4" s="75" t="s">
         <v>110</v>
       </c>
-      <c r="I4" s="80" t="s">
+      <c r="I4" s="75" t="s">
         <v>105</v>
       </c>
-      <c r="J4" s="79" t="s">
+      <c r="J4" s="74" t="s">
         <v>106</v>
       </c>
-      <c r="K4" s="98" t="s">
+      <c r="K4" s="93" t="s">
         <v>107</v>
       </c>
-      <c r="L4" s="68"/>
+      <c r="L4" s="63"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B5" s="3" t="s">
@@ -6589,13 +6826,13 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8ABB60C7-E45F-43AB-8437-9988EA9E799C}">
           <x14:formula1>
-            <xm:f>CategoryList!$B$31:$B$34</xm:f>
+            <xm:f>CategoryList!$B$34:$B$37</xm:f>
           </x14:formula1>
           <xm:sqref>F5:F1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C44F4EB6-264F-4B81-BCA8-F8210AC2E982}">
           <x14:formula1>
-            <xm:f>CategoryList!$B$24:$B$28</xm:f>
+            <xm:f>CategoryList!$B$27:$B$31</xm:f>
           </x14:formula1>
           <xm:sqref>I4:I1048576</xm:sqref>
         </x14:dataValidation>
@@ -6629,86 +6866,86 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2" s="6"/>
-      <c r="B2" s="170" t="s">
+      <c r="B2" s="143" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="170"/>
-      <c r="D2" s="171"/>
-      <c r="E2" s="145" t="s">
+      <c r="C2" s="143"/>
+      <c r="D2" s="144"/>
+      <c r="E2" s="162" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="146"/>
-      <c r="G2" s="146"/>
-      <c r="H2" s="146"/>
-      <c r="I2" s="146"/>
-      <c r="J2" s="146"/>
-      <c r="K2" s="147"/>
+      <c r="F2" s="163"/>
+      <c r="G2" s="163"/>
+      <c r="H2" s="163"/>
+      <c r="I2" s="163"/>
+      <c r="J2" s="163"/>
+      <c r="K2" s="164"/>
       <c r="L2" s="5"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3" s="6"/>
-      <c r="B3" s="75" t="s">
+      <c r="B3" s="70" t="s">
         <v>153</v>
       </c>
-      <c r="C3" s="87" t="s">
+      <c r="C3" s="82" t="s">
         <v>232</v>
       </c>
-      <c r="D3" s="76" t="s">
+      <c r="D3" s="71" t="s">
         <v>160</v>
       </c>
-      <c r="E3" s="71" t="s">
+      <c r="E3" s="66" t="s">
         <v>174</v>
       </c>
-      <c r="F3" s="72" t="s">
+      <c r="F3" s="67" t="s">
         <v>175</v>
       </c>
-      <c r="G3" s="72" t="s">
+      <c r="G3" s="67" t="s">
         <v>176</v>
       </c>
-      <c r="H3" s="72" t="s">
+      <c r="H3" s="67" t="s">
         <v>177</v>
       </c>
-      <c r="I3" s="72" t="s">
+      <c r="I3" s="67" t="s">
         <v>178</v>
       </c>
-      <c r="J3" s="72" t="s">
+      <c r="J3" s="67" t="s">
         <v>179</v>
       </c>
-      <c r="K3" s="73" t="s">
+      <c r="K3" s="68" t="s">
         <v>180</v>
       </c>
       <c r="L3" s="5"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4" s="6"/>
-      <c r="B4" s="105" t="s">
+      <c r="B4" s="100" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="125" t="s">
+      <c r="C4" s="120" t="s">
         <v>231</v>
       </c>
-      <c r="D4" s="103" t="s">
+      <c r="D4" s="98" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="106" t="s">
+      <c r="E4" s="101" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="106" t="s">
+      <c r="F4" s="101" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="106" t="s">
+      <c r="G4" s="101" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="106" t="s">
+      <c r="H4" s="101" t="s">
         <v>14</v>
       </c>
-      <c r="I4" s="106" t="s">
+      <c r="I4" s="101" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="106" t="s">
+      <c r="J4" s="101" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="107" t="s">
+      <c r="K4" s="102" t="s">
         <v>12</v>
       </c>
       <c r="L4" s="5"/>
@@ -6938,7 +7175,7 @@
       </c>
     </row>
     <row r="18" spans="7:7" x14ac:dyDescent="0.4">
-      <c r="G18" s="127"/>
+      <c r="G18" s="122"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6998,12 +7235,12 @@
   <cols>
     <col min="2" max="2" width="9.375" customWidth="1"/>
     <col min="3" max="4" width="15.25" customWidth="1"/>
-    <col min="5" max="5" width="13.25" style="120" customWidth="1"/>
-    <col min="6" max="6" width="14.125" style="120" customWidth="1"/>
-    <col min="7" max="7" width="14.25" style="120" customWidth="1"/>
-    <col min="8" max="8" width="17.5" style="120" customWidth="1"/>
-    <col min="9" max="9" width="14.75" style="120" customWidth="1"/>
-    <col min="10" max="10" width="18.375" style="120" customWidth="1"/>
+    <col min="5" max="5" width="13.25" style="115" customWidth="1"/>
+    <col min="6" max="6" width="14.125" style="115" customWidth="1"/>
+    <col min="7" max="7" width="14.25" style="115" customWidth="1"/>
+    <col min="8" max="8" width="17.5" style="115" customWidth="1"/>
+    <col min="9" max="9" width="14.75" style="115" customWidth="1"/>
+    <col min="10" max="10" width="18.375" style="115" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" x14ac:dyDescent="0.4">
@@ -7018,75 +7255,75 @@
       <c r="J1"/>
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B2" s="176" t="s">
+      <c r="B2" s="174" t="s">
         <v>190</v>
       </c>
-      <c r="C2" s="177"/>
-      <c r="D2" s="166"/>
-      <c r="E2" s="151" t="s">
+      <c r="C2" s="175"/>
+      <c r="D2" s="168"/>
+      <c r="E2" s="147" t="s">
         <v>198</v>
       </c>
-      <c r="F2" s="152"/>
-      <c r="G2" s="152"/>
-      <c r="H2" s="152"/>
-      <c r="I2" s="152"/>
-      <c r="J2" s="152"/>
+      <c r="F2" s="148"/>
+      <c r="G2" s="148"/>
+      <c r="H2" s="148"/>
+      <c r="I2" s="148"/>
+      <c r="J2" s="148"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B3" s="134" t="s">
+      <c r="B3" s="129" t="s">
         <v>274</v>
       </c>
-      <c r="C3" s="81" t="s">
+      <c r="C3" s="76" t="s">
         <v>133</v>
       </c>
-      <c r="D3" s="130" t="s">
+      <c r="D3" s="125" t="s">
         <v>232</v>
       </c>
-      <c r="E3" s="82" t="s">
+      <c r="E3" s="77" t="s">
         <v>192</v>
       </c>
-      <c r="F3" s="82" t="s">
+      <c r="F3" s="77" t="s">
         <v>193</v>
       </c>
-      <c r="G3" s="82" t="s">
+      <c r="G3" s="77" t="s">
         <v>194</v>
       </c>
-      <c r="H3" s="82" t="s">
+      <c r="H3" s="77" t="s">
         <v>195</v>
       </c>
-      <c r="I3" s="82" t="s">
+      <c r="I3" s="77" t="s">
         <v>196</v>
       </c>
-      <c r="J3" s="82" t="s">
+      <c r="J3" s="77" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B4" s="103" t="s">
+      <c r="B4" s="98" t="s">
         <v>275</v>
       </c>
       <c r="C4" s="24" t="s">
         <v>191</v>
       </c>
-      <c r="D4" s="125" t="s">
+      <c r="D4" s="120" t="s">
         <v>231</v>
       </c>
-      <c r="E4" s="77" t="s">
+      <c r="E4" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="77" t="s">
+      <c r="F4" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="79" t="s">
+      <c r="G4" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="80" t="s">
+      <c r="H4" s="75" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="79" t="s">
+      <c r="I4" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="J4" s="79" t="s">
+      <c r="J4" s="74" t="s">
         <v>25</v>
       </c>
     </row>
@@ -7100,22 +7337,22 @@
       <c r="D5">
         <v>6</v>
       </c>
-      <c r="E5" s="119">
+      <c r="E5" s="114">
         <v>1.2</v>
       </c>
-      <c r="F5" s="119">
+      <c r="F5" s="114">
         <v>1.2</v>
       </c>
-      <c r="G5" s="119">
+      <c r="G5" s="114">
         <v>1.2</v>
       </c>
-      <c r="H5" s="119">
+      <c r="H5" s="114">
         <v>1.2</v>
       </c>
-      <c r="I5" s="119">
+      <c r="I5" s="114">
         <v>1.2</v>
       </c>
-      <c r="J5" s="119">
+      <c r="J5" s="114">
         <v>1.2</v>
       </c>
     </row>
@@ -7123,28 +7360,28 @@
       <c r="B6" s="28" t="s">
         <v>276</v>
       </c>
-      <c r="C6" s="131" t="s">
+      <c r="C6" s="126" t="s">
         <v>186</v>
       </c>
       <c r="D6" s="28">
         <v>6</v>
       </c>
-      <c r="E6" s="126">
+      <c r="E6" s="121">
         <v>1.2</v>
       </c>
-      <c r="F6" s="119">
+      <c r="F6" s="114">
         <v>1</v>
       </c>
-      <c r="G6" s="119">
+      <c r="G6" s="114">
         <v>1.2</v>
       </c>
-      <c r="H6" s="119">
+      <c r="H6" s="114">
         <v>0.8</v>
       </c>
-      <c r="I6" s="119">
+      <c r="I6" s="114">
         <v>1.1000000000000001</v>
       </c>
-      <c r="J6" s="119">
+      <c r="J6" s="114">
         <v>1</v>
       </c>
     </row>
@@ -7152,28 +7389,28 @@
       <c r="B7" s="28" t="s">
         <v>277</v>
       </c>
-      <c r="C7" s="131" t="s">
+      <c r="C7" s="126" t="s">
         <v>187</v>
       </c>
       <c r="D7" s="28">
         <v>6</v>
       </c>
-      <c r="E7" s="126">
+      <c r="E7" s="121">
         <v>1.2</v>
       </c>
-      <c r="F7" s="119">
+      <c r="F7" s="114">
         <v>1</v>
       </c>
-      <c r="G7" s="119">
+      <c r="G7" s="114">
         <v>1.2</v>
       </c>
-      <c r="H7" s="119">
+      <c r="H7" s="114">
         <v>0.8</v>
       </c>
-      <c r="I7" s="119">
+      <c r="I7" s="114">
         <v>1.1000000000000001</v>
       </c>
-      <c r="J7" s="119">
+      <c r="J7" s="114">
         <v>1</v>
       </c>
     </row>
@@ -7181,28 +7418,28 @@
       <c r="B8" s="28" t="s">
         <v>278</v>
       </c>
-      <c r="C8" s="132" t="s">
+      <c r="C8" s="127" t="s">
         <v>188</v>
       </c>
       <c r="D8" s="28">
         <v>6</v>
       </c>
-      <c r="E8" s="126">
+      <c r="E8" s="121">
         <v>1</v>
       </c>
-      <c r="F8" s="119">
+      <c r="F8" s="114">
         <v>1.2</v>
       </c>
-      <c r="G8" s="119">
+      <c r="G8" s="114">
         <v>1</v>
       </c>
-      <c r="H8" s="119">
+      <c r="H8" s="114">
         <v>1.3</v>
       </c>
-      <c r="I8" s="119">
+      <c r="I8" s="114">
         <v>1</v>
       </c>
-      <c r="J8" s="119">
+      <c r="J8" s="114">
         <v>1.4</v>
       </c>
     </row>
@@ -7210,28 +7447,28 @@
       <c r="B9" s="28" t="s">
         <v>279</v>
       </c>
-      <c r="C9" s="133" t="s">
+      <c r="C9" s="128" t="s">
         <v>189</v>
       </c>
       <c r="D9" s="28">
         <v>6</v>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="121">
         <v>1.2</v>
       </c>
-      <c r="F9" s="119">
+      <c r="F9" s="114">
         <v>1</v>
       </c>
-      <c r="G9" s="119">
+      <c r="G9" s="114">
         <v>1.2</v>
       </c>
-      <c r="H9" s="119">
+      <c r="H9" s="114">
         <v>2</v>
       </c>
-      <c r="I9" s="119">
+      <c r="I9" s="114">
         <v>1.1000000000000001</v>
       </c>
-      <c r="J9" s="119">
+      <c r="J9" s="114">
         <v>1</v>
       </c>
     </row>
@@ -7261,20 +7498,20 @@
       </c>
     </row>
     <row r="2" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B2" s="178" t="s">
+      <c r="B2" s="176" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="179"/>
-      <c r="D2" s="180"/>
+      <c r="C2" s="177"/>
+      <c r="D2" s="178"/>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B3" s="103" t="s">
+      <c r="B3" s="98" t="s">
         <v>131</v>
       </c>
-      <c r="C3" s="103" t="s">
+      <c r="C3" s="98" t="s">
         <v>133</v>
       </c>
-      <c r="D3" s="103" t="s">
+      <c r="D3" s="98" t="s">
         <v>254</v>
       </c>
     </row>
